--- a/Pregame/1. ELICITACION/1.3 HISTORIA DE USUSARIO/G4_HistoriasDeUsuario_A13_(Final)29022 .xlsx
+++ b/Pregame/1. ELICITACION/1.3 HISTORIA DE USUSARIO/G4_HistoriasDeUsuario_A13_(Final)29022 .xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Desktop\29022_G4_METDS\Pregame\1. ELICITACION\1.3 HISTORIA DE USUSARIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63801B82-E173-48DE-BAA8-2484881D08EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB1C9BB6-0F89-479C-98DF-82D5C23196AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1104,119 +1104,6 @@
     <xf numFmtId="14" fontId="18" fillId="10" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1242,6 +1129,119 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1657,22 +1657,22 @@
     </row>
     <row r="3" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="107"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="68"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
@@ -1715,46 +1715,46 @@
     </row>
     <row r="5" spans="1:26" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="108" t="s">
+      <c r="B5" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="108" t="s">
+      <c r="C5" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="108" t="s">
+      <c r="D5" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="108" t="s">
+      <c r="E5" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="108" t="s">
+      <c r="F5" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="108" t="s">
+      <c r="G5" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="108" t="s">
+      <c r="H5" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="108" t="s">
+      <c r="I5" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="108" t="s">
+      <c r="J5" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="108" t="s">
+      <c r="K5" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="108" t="s">
+      <c r="L5" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="108" t="s">
+      <c r="M5" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="108" t="s">
+      <c r="N5" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="O5" s="108" t="s">
+      <c r="O5" s="57" t="s">
         <v>14</v>
       </c>
       <c r="P5" s="1"/>
@@ -1771,7 +1771,7 @@
     </row>
     <row r="6" spans="1:26" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
-      <c r="B6" s="109" t="s">
+      <c r="B6" s="58" t="s">
         <v>53</v>
       </c>
       <c r="C6" s="49" t="s">
@@ -1825,7 +1825,7 @@
     </row>
     <row r="7" spans="1:26" ht="183" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
-      <c r="B7" s="110" t="s">
+      <c r="B7" s="59" t="s">
         <v>54</v>
       </c>
       <c r="C7" s="49" t="s">
@@ -1879,7 +1879,7 @@
     </row>
     <row r="8" spans="1:26" ht="138" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
-      <c r="B8" s="111" t="s">
+      <c r="B8" s="60" t="s">
         <v>55</v>
       </c>
       <c r="C8" s="51" t="s">
@@ -1933,7 +1933,7 @@
     </row>
     <row r="9" spans="1:26" ht="138" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="112" t="s">
+      <c r="B9" s="61" t="s">
         <v>78</v>
       </c>
       <c r="C9" s="55" t="s">
@@ -1987,7 +1987,7 @@
     </row>
     <row r="10" spans="1:26" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
-      <c r="B10" s="113" t="s">
+      <c r="B10" s="62" t="s">
         <v>64</v>
       </c>
       <c r="C10" s="51" t="s">
@@ -2041,7 +2041,7 @@
     </row>
     <row r="11" spans="1:26" ht="118.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="114" t="s">
+      <c r="B11" s="63" t="s">
         <v>63</v>
       </c>
       <c r="C11" s="53" t="s">
@@ -2094,7 +2094,7 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="122.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="115" t="s">
+      <c r="B12" s="64" t="s">
         <v>65</v>
       </c>
       <c r="C12" s="49" t="s">
@@ -2137,7 +2137,7 @@
     </row>
     <row r="13" spans="1:26" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
-      <c r="B13" s="116" t="s">
+      <c r="B13" s="65" t="s">
         <v>72</v>
       </c>
       <c r="C13" s="49" t="s">
@@ -29914,23 +29914,23 @@
       <c r="F5" s="17"/>
     </row>
     <row r="6" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="94" t="s">
+      <c r="B6" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="57"/>
-      <c r="O6" s="57"/>
-      <c r="P6" s="58"/>
+      <c r="C6" s="85"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="85"/>
+      <c r="H6" s="85"/>
+      <c r="I6" s="85"/>
+      <c r="J6" s="85"/>
+      <c r="K6" s="85"/>
+      <c r="L6" s="85"/>
+      <c r="M6" s="85"/>
+      <c r="N6" s="85"/>
+      <c r="O6" s="85"/>
+      <c r="P6" s="86"/>
     </row>
     <row r="7" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18"/>
@@ -29984,15 +29984,15 @@
         <v>1</v>
       </c>
       <c r="D9" s="27"/>
-      <c r="E9" s="92" t="s">
+      <c r="E9" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="58"/>
+      <c r="F9" s="86"/>
       <c r="G9" s="27"/>
-      <c r="H9" s="92" t="s">
+      <c r="H9" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="58"/>
+      <c r="I9" s="86"/>
       <c r="J9" s="28"/>
       <c r="K9" s="28"/>
       <c r="L9" s="28"/>
@@ -30008,17 +30008,17 @@
         <v>53</v>
       </c>
       <c r="D10" s="31"/>
-      <c r="E10" s="93" t="str">
+      <c r="E10" s="88" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,5,0)</f>
         <v>Administrador</v>
       </c>
-      <c r="F10" s="58"/>
+      <c r="F10" s="86"/>
       <c r="G10" s="32"/>
-      <c r="H10" s="93" t="str">
+      <c r="H10" s="88" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,11,0)</f>
         <v>Terminado</v>
       </c>
-      <c r="I10" s="58"/>
+      <c r="I10" s="86"/>
       <c r="J10" s="32"/>
       <c r="K10" s="28"/>
       <c r="L10" s="28"/>
@@ -30063,15 +30063,15 @@
         <v>25</v>
       </c>
       <c r="D12" s="31"/>
-      <c r="E12" s="92" t="s">
+      <c r="E12" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="58"/>
+      <c r="F12" s="86"/>
       <c r="G12" s="32"/>
-      <c r="H12" s="92" t="s">
+      <c r="H12" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="58"/>
+      <c r="I12" s="86"/>
       <c r="J12" s="32"/>
       <c r="K12" s="34"/>
       <c r="L12" s="34"/>
@@ -30098,17 +30098,17 @@
         <v>6</v>
       </c>
       <c r="D13" s="31"/>
-      <c r="E13" s="93" t="str">
+      <c r="E13" s="88" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,10,0)</f>
         <v>Alta</v>
       </c>
-      <c r="F13" s="58"/>
+      <c r="F13" s="86"/>
       <c r="G13" s="32"/>
-      <c r="H13" s="93" t="str">
+      <c r="H13" s="88" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,7,0)</f>
         <v>Kevin Castillo</v>
       </c>
-      <c r="I13" s="58"/>
+      <c r="I13" s="86"/>
       <c r="J13" s="32"/>
       <c r="K13" s="34"/>
       <c r="L13" s="34"/>
@@ -30158,34 +30158,34 @@
     <row r="15" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="25"/>
-      <c r="C15" s="81" t="s">
+      <c r="C15" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="79" t="str">
+      <c r="D15" s="89" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,3,0)</f>
         <v>El programa debe Validar credenciales de usuario mediante autenticación</v>
       </c>
-      <c r="E15" s="71"/>
+      <c r="E15" s="90"/>
       <c r="F15" s="35"/>
-      <c r="G15" s="81" t="s">
+      <c r="G15" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="79" t="str">
+      <c r="H15" s="89" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,4,0)</f>
         <v>Garantizar que solo personal autorizado acceda al sistema</v>
       </c>
-      <c r="I15" s="77"/>
-      <c r="J15" s="71"/>
+      <c r="I15" s="98"/>
+      <c r="J15" s="90"/>
       <c r="K15" s="35"/>
-      <c r="L15" s="81" t="s">
+      <c r="L15" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="M15" s="84" t="str">
+      <c r="M15" s="100" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,6,0)</f>
         <v>Diseñar formulario de login con campos usuario/contraseña, implementar validación de credenciales en base de datos.</v>
       </c>
-      <c r="N15" s="77"/>
-      <c r="O15" s="71"/>
+      <c r="N15" s="98"/>
+      <c r="O15" s="90"/>
       <c r="P15" s="29"/>
       <c r="Q15" s="18"/>
       <c r="R15" s="18"/>
@@ -30201,19 +30201,19 @@
     <row r="16" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="18"/>
       <c r="B16" s="25"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="72"/>
-      <c r="E16" s="73"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="91"/>
+      <c r="E16" s="92"/>
       <c r="F16" s="35"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="72"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="73"/>
+      <c r="G16" s="96"/>
+      <c r="H16" s="91"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="92"/>
       <c r="K16" s="35"/>
-      <c r="L16" s="82"/>
-      <c r="M16" s="72"/>
-      <c r="N16" s="60"/>
-      <c r="O16" s="73"/>
+      <c r="L16" s="96"/>
+      <c r="M16" s="91"/>
+      <c r="N16" s="70"/>
+      <c r="O16" s="92"/>
       <c r="P16" s="29"/>
       <c r="Q16" s="18"/>
       <c r="R16" s="18"/>
@@ -30229,19 +30229,19 @@
     <row r="17" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18"/>
       <c r="B17" s="25"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="75"/>
+      <c r="C17" s="97"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="94"/>
       <c r="F17" s="35"/>
-      <c r="G17" s="83"/>
-      <c r="H17" s="74"/>
-      <c r="I17" s="78"/>
-      <c r="J17" s="75"/>
+      <c r="G17" s="97"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="99"/>
+      <c r="J17" s="94"/>
       <c r="K17" s="35"/>
-      <c r="L17" s="83"/>
-      <c r="M17" s="74"/>
-      <c r="N17" s="78"/>
-      <c r="O17" s="75"/>
+      <c r="L17" s="97"/>
+      <c r="M17" s="93"/>
+      <c r="N17" s="99"/>
+      <c r="O17" s="94"/>
       <c r="P17" s="29"/>
       <c r="Q17" s="18"/>
       <c r="R17" s="18"/>
@@ -30284,42 +30284,42 @@
     </row>
     <row r="19" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="25"/>
-      <c r="C19" s="91" t="s">
+      <c r="C19" s="107" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="71"/>
-      <c r="E19" s="85" t="str">
+      <c r="D19" s="90"/>
+      <c r="E19" s="101" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,14,0)</f>
         <v xml:space="preserve">Inicio de Sesión </v>
       </c>
-      <c r="F19" s="86"/>
-      <c r="G19" s="86"/>
-      <c r="H19" s="86"/>
-      <c r="I19" s="86"/>
-      <c r="J19" s="86"/>
-      <c r="K19" s="86"/>
-      <c r="L19" s="86"/>
-      <c r="M19" s="86"/>
-      <c r="N19" s="86"/>
-      <c r="O19" s="87"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="102"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="102"/>
+      <c r="K19" s="102"/>
+      <c r="L19" s="102"/>
+      <c r="M19" s="102"/>
+      <c r="N19" s="102"/>
+      <c r="O19" s="103"/>
       <c r="P19" s="29"/>
       <c r="Q19" s="18"/>
     </row>
     <row r="20" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="25"/>
-      <c r="C20" s="74"/>
-      <c r="D20" s="75"/>
-      <c r="E20" s="88"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="89"/>
-      <c r="J20" s="89"/>
-      <c r="K20" s="89"/>
-      <c r="L20" s="89"/>
-      <c r="M20" s="89"/>
-      <c r="N20" s="89"/>
-      <c r="O20" s="90"/>
+      <c r="C20" s="93"/>
+      <c r="D20" s="94"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="105"/>
+      <c r="H20" s="105"/>
+      <c r="I20" s="105"/>
+      <c r="J20" s="105"/>
+      <c r="K20" s="105"/>
+      <c r="L20" s="105"/>
+      <c r="M20" s="105"/>
+      <c r="N20" s="105"/>
+      <c r="O20" s="106"/>
       <c r="P20" s="29"/>
       <c r="Q20" s="18"/>
     </row>
@@ -30344,29 +30344,29 @@
     <row r="22" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18"/>
       <c r="B22" s="25"/>
-      <c r="C22" s="70" t="s">
+      <c r="C22" s="108" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="71"/>
-      <c r="E22" s="76" t="str">
+      <c r="D22" s="90"/>
+      <c r="E22" s="109" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,12,0)</f>
         <v>Ingresar credenciales correctas y verificar acceso, ingresar credenciales incorrectas y verificar mensaje de error, verificar que la contraseña se muestre enmascarada</v>
       </c>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="71"/>
+      <c r="F22" s="98"/>
+      <c r="G22" s="98"/>
+      <c r="H22" s="90"/>
       <c r="I22" s="28"/>
-      <c r="J22" s="70" t="s">
+      <c r="J22" s="108" t="s">
         <v>13</v>
       </c>
-      <c r="K22" s="71"/>
-      <c r="L22" s="79">
+      <c r="K22" s="90"/>
+      <c r="L22" s="89">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,13,0)</f>
         <v>0</v>
       </c>
-      <c r="M22" s="77"/>
-      <c r="N22" s="77"/>
-      <c r="O22" s="71"/>
+      <c r="M22" s="98"/>
+      <c r="N22" s="98"/>
+      <c r="O22" s="90"/>
       <c r="P22" s="29"/>
       <c r="Q22" s="18"/>
       <c r="R22" s="18"/>
@@ -30382,19 +30382,19 @@
     <row r="23" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18"/>
       <c r="B23" s="25"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="73"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="92"/>
       <c r="I23" s="28"/>
-      <c r="J23" s="72"/>
-      <c r="K23" s="73"/>
-      <c r="L23" s="72"/>
-      <c r="M23" s="60"/>
-      <c r="N23" s="60"/>
-      <c r="O23" s="73"/>
+      <c r="J23" s="91"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="91"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="70"/>
+      <c r="O23" s="92"/>
       <c r="P23" s="29"/>
       <c r="Q23" s="18"/>
       <c r="R23" s="18"/>
@@ -30410,19 +30410,19 @@
     <row r="24" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18"/>
       <c r="B24" s="25"/>
-      <c r="C24" s="74"/>
-      <c r="D24" s="75"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="78"/>
-      <c r="G24" s="78"/>
-      <c r="H24" s="75"/>
+      <c r="C24" s="93"/>
+      <c r="D24" s="94"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="99"/>
+      <c r="H24" s="94"/>
       <c r="I24" s="28"/>
-      <c r="J24" s="74"/>
-      <c r="K24" s="75"/>
-      <c r="L24" s="74"/>
-      <c r="M24" s="78"/>
-      <c r="N24" s="78"/>
-      <c r="O24" s="75"/>
+      <c r="J24" s="93"/>
+      <c r="K24" s="94"/>
+      <c r="L24" s="93"/>
+      <c r="M24" s="99"/>
+      <c r="N24" s="99"/>
+      <c r="O24" s="94"/>
       <c r="P24" s="29"/>
       <c r="Q24" s="18"/>
       <c r="R24" s="18"/>
@@ -30481,21 +30481,21 @@
     </row>
     <row r="27" spans="1:26" ht="21" x14ac:dyDescent="0.25">
       <c r="A27" s="18"/>
-      <c r="B27" s="80"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="60"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="60"/>
-      <c r="J27" s="60"/>
-      <c r="K27" s="60"/>
-      <c r="L27" s="60"/>
-      <c r="M27" s="60"/>
-      <c r="N27" s="60"/>
-      <c r="O27" s="60"/>
-      <c r="P27" s="60"/>
+      <c r="B27" s="110"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="70"/>
+      <c r="M27" s="70"/>
+      <c r="N27" s="70"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="70"/>
       <c r="Q27" s="18"/>
       <c r="R27" s="18"/>
       <c r="S27" s="18"/>
@@ -30566,11 +30566,11 @@
       <c r="B30" s="18"/>
       <c r="C30" s="39"/>
       <c r="D30" s="40"/>
-      <c r="E30" s="63"/>
-      <c r="F30" s="60"/>
+      <c r="E30" s="111"/>
+      <c r="F30" s="70"/>
       <c r="G30" s="40"/>
-      <c r="H30" s="63"/>
-      <c r="I30" s="60"/>
+      <c r="H30" s="111"/>
+      <c r="I30" s="70"/>
       <c r="J30" s="18"/>
       <c r="K30" s="18"/>
       <c r="L30" s="18"/>
@@ -30594,11 +30594,11 @@
       <c r="B31" s="18"/>
       <c r="C31" s="39"/>
       <c r="D31" s="41"/>
-      <c r="E31" s="63"/>
-      <c r="F31" s="60"/>
+      <c r="E31" s="111"/>
+      <c r="F31" s="70"/>
       <c r="G31" s="42"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="60"/>
+      <c r="H31" s="111"/>
+      <c r="I31" s="70"/>
       <c r="J31" s="42"/>
       <c r="K31" s="43"/>
       <c r="L31" s="43"/>
@@ -30622,11 +30622,11 @@
       <c r="B32" s="18"/>
       <c r="C32" s="44"/>
       <c r="D32" s="41"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="60"/>
+      <c r="E32" s="114"/>
+      <c r="F32" s="70"/>
       <c r="G32" s="42"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="60"/>
+      <c r="H32" s="114"/>
+      <c r="I32" s="70"/>
       <c r="J32" s="42"/>
       <c r="K32" s="43"/>
       <c r="L32" s="43"/>
@@ -30656,55 +30656,55 @@
     <row r="34" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="18"/>
       <c r="B34" s="18"/>
-      <c r="C34" s="63"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="60"/>
+      <c r="C34" s="111"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="70"/>
       <c r="F34" s="45"/>
-      <c r="G34" s="63"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="60"/>
-      <c r="J34" s="60"/>
+      <c r="G34" s="111"/>
+      <c r="H34" s="74"/>
+      <c r="I34" s="70"/>
+      <c r="J34" s="70"/>
       <c r="K34" s="45"/>
-      <c r="L34" s="63"/>
-      <c r="M34" s="68"/>
-      <c r="N34" s="60"/>
-      <c r="O34" s="60"/>
+      <c r="L34" s="111"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="70"/>
+      <c r="O34" s="70"/>
       <c r="P34" s="18"/>
     </row>
     <row r="35" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="18"/>
       <c r="B35" s="18"/>
-      <c r="C35" s="60"/>
-      <c r="D35" s="60"/>
-      <c r="E35" s="60"/>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
       <c r="F35" s="45"/>
-      <c r="G35" s="60"/>
-      <c r="H35" s="60"/>
-      <c r="I35" s="60"/>
-      <c r="J35" s="60"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="70"/>
       <c r="K35" s="45"/>
-      <c r="L35" s="60"/>
-      <c r="M35" s="60"/>
-      <c r="N35" s="60"/>
-      <c r="O35" s="60"/>
+      <c r="L35" s="70"/>
+      <c r="M35" s="70"/>
+      <c r="N35" s="70"/>
+      <c r="O35" s="70"/>
       <c r="P35" s="18"/>
     </row>
     <row r="36" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="18"/>
       <c r="B36" s="18"/>
-      <c r="C36" s="60"/>
-      <c r="D36" s="60"/>
-      <c r="E36" s="60"/>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
       <c r="F36" s="45"/>
-      <c r="G36" s="60"/>
-      <c r="H36" s="60"/>
-      <c r="I36" s="60"/>
-      <c r="J36" s="60"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="70"/>
       <c r="K36" s="45"/>
-      <c r="L36" s="60"/>
-      <c r="M36" s="60"/>
-      <c r="N36" s="60"/>
-      <c r="O36" s="60"/>
+      <c r="L36" s="70"/>
+      <c r="M36" s="70"/>
+      <c r="N36" s="70"/>
+      <c r="O36" s="70"/>
       <c r="P36" s="18"/>
     </row>
     <row r="37" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -30727,36 +30727,36 @@
     </row>
     <row r="38" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18"/>
-      <c r="C38" s="67"/>
-      <c r="D38" s="60"/>
-      <c r="E38" s="69"/>
-      <c r="F38" s="60"/>
-      <c r="G38" s="60"/>
-      <c r="H38" s="60"/>
-      <c r="I38" s="60"/>
-      <c r="J38" s="60"/>
-      <c r="K38" s="60"/>
-      <c r="L38" s="60"/>
-      <c r="M38" s="60"/>
-      <c r="N38" s="60"/>
-      <c r="O38" s="60"/>
+      <c r="C38" s="115"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="113"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="70"/>
       <c r="P38" s="18"/>
     </row>
     <row r="39" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18"/>
-      <c r="C39" s="60"/>
-      <c r="D39" s="60"/>
-      <c r="E39" s="60"/>
-      <c r="F39" s="60"/>
-      <c r="G39" s="60"/>
-      <c r="H39" s="60"/>
-      <c r="I39" s="60"/>
-      <c r="J39" s="60"/>
-      <c r="K39" s="60"/>
-      <c r="L39" s="60"/>
-      <c r="M39" s="60"/>
-      <c r="N39" s="60"/>
-      <c r="O39" s="60"/>
+      <c r="C39" s="70"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="70"/>
+      <c r="M39" s="70"/>
+      <c r="N39" s="70"/>
+      <c r="O39" s="70"/>
       <c r="P39" s="18"/>
     </row>
     <row r="40" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -30779,55 +30779,55 @@
     <row r="41" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="18"/>
       <c r="B41" s="18"/>
-      <c r="C41" s="63"/>
-      <c r="D41" s="60"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="60"/>
-      <c r="G41" s="60"/>
-      <c r="H41" s="60"/>
+      <c r="C41" s="111"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="116"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="70"/>
       <c r="I41" s="18"/>
-      <c r="J41" s="63"/>
-      <c r="K41" s="60"/>
-      <c r="L41" s="64"/>
-      <c r="M41" s="60"/>
-      <c r="N41" s="60"/>
-      <c r="O41" s="60"/>
+      <c r="J41" s="111"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="74"/>
+      <c r="M41" s="70"/>
+      <c r="N41" s="70"/>
+      <c r="O41" s="70"/>
       <c r="P41" s="18"/>
     </row>
     <row r="42" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="18"/>
       <c r="B42" s="18"/>
-      <c r="C42" s="60"/>
-      <c r="D42" s="60"/>
-      <c r="E42" s="60"/>
-      <c r="F42" s="60"/>
-      <c r="G42" s="60"/>
-      <c r="H42" s="60"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
       <c r="I42" s="18"/>
-      <c r="J42" s="60"/>
-      <c r="K42" s="60"/>
-      <c r="L42" s="60"/>
-      <c r="M42" s="60"/>
-      <c r="N42" s="60"/>
-      <c r="O42" s="60"/>
+      <c r="J42" s="70"/>
+      <c r="K42" s="70"/>
+      <c r="L42" s="70"/>
+      <c r="M42" s="70"/>
+      <c r="N42" s="70"/>
+      <c r="O42" s="70"/>
       <c r="P42" s="18"/>
     </row>
     <row r="43" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="18"/>
       <c r="B43" s="18"/>
-      <c r="C43" s="60"/>
-      <c r="D43" s="60"/>
-      <c r="E43" s="60"/>
-      <c r="F43" s="60"/>
-      <c r="G43" s="60"/>
-      <c r="H43" s="60"/>
+      <c r="C43" s="70"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="70"/>
+      <c r="F43" s="70"/>
+      <c r="G43" s="70"/>
+      <c r="H43" s="70"/>
       <c r="I43" s="18"/>
-      <c r="J43" s="60"/>
-      <c r="K43" s="60"/>
-      <c r="L43" s="60"/>
-      <c r="M43" s="60"/>
-      <c r="N43" s="60"/>
-      <c r="O43" s="60"/>
+      <c r="J43" s="70"/>
+      <c r="K43" s="70"/>
+      <c r="L43" s="70"/>
+      <c r="M43" s="70"/>
+      <c r="N43" s="70"/>
+      <c r="O43" s="70"/>
       <c r="P43" s="18"/>
     </row>
     <row r="44" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -30868,21 +30868,21 @@
     </row>
     <row r="46" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="18"/>
-      <c r="B46" s="65"/>
-      <c r="C46" s="60"/>
-      <c r="D46" s="60"/>
-      <c r="E46" s="60"/>
-      <c r="F46" s="60"/>
-      <c r="G46" s="60"/>
-      <c r="H46" s="60"/>
-      <c r="I46" s="60"/>
-      <c r="J46" s="60"/>
-      <c r="K46" s="60"/>
-      <c r="L46" s="60"/>
-      <c r="M46" s="60"/>
-      <c r="N46" s="60"/>
-      <c r="O46" s="60"/>
-      <c r="P46" s="60"/>
+      <c r="B46" s="77"/>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="70"/>
+      <c r="K46" s="70"/>
+      <c r="L46" s="70"/>
+      <c r="M46" s="70"/>
+      <c r="N46" s="70"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="70"/>
     </row>
     <row r="47" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="18"/>
@@ -30925,11 +30925,11 @@
       <c r="B49" s="18"/>
       <c r="C49" s="46"/>
       <c r="D49" s="18"/>
-      <c r="E49" s="62"/>
-      <c r="F49" s="60"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="70"/>
       <c r="G49" s="18"/>
-      <c r="H49" s="62"/>
-      <c r="I49" s="60"/>
+      <c r="H49" s="69"/>
+      <c r="I49" s="70"/>
       <c r="J49" s="18"/>
       <c r="K49" s="18"/>
       <c r="L49" s="18"/>
@@ -30943,11 +30943,11 @@
       <c r="B50" s="18"/>
       <c r="C50" s="47"/>
       <c r="D50" s="18"/>
-      <c r="E50" s="59"/>
-      <c r="F50" s="60"/>
+      <c r="E50" s="79"/>
+      <c r="F50" s="70"/>
       <c r="G50" s="18"/>
-      <c r="H50" s="61"/>
-      <c r="I50" s="60"/>
+      <c r="H50" s="114"/>
+      <c r="I50" s="70"/>
       <c r="J50" s="18"/>
       <c r="K50" s="18"/>
       <c r="L50" s="18"/>
@@ -30979,11 +30979,11 @@
       <c r="B52" s="18"/>
       <c r="C52" s="46"/>
       <c r="D52" s="18"/>
-      <c r="E52" s="62"/>
-      <c r="F52" s="60"/>
+      <c r="E52" s="69"/>
+      <c r="F52" s="70"/>
       <c r="G52" s="18"/>
-      <c r="H52" s="62"/>
-      <c r="I52" s="60"/>
+      <c r="H52" s="69"/>
+      <c r="I52" s="70"/>
       <c r="J52" s="18"/>
       <c r="K52" s="18"/>
       <c r="L52" s="18"/>
@@ -30997,11 +30997,11 @@
       <c r="B53" s="18"/>
       <c r="C53" s="47"/>
       <c r="D53" s="18"/>
-      <c r="E53" s="59"/>
-      <c r="F53" s="60"/>
+      <c r="E53" s="79"/>
+      <c r="F53" s="70"/>
       <c r="G53" s="18"/>
-      <c r="H53" s="59"/>
-      <c r="I53" s="60"/>
+      <c r="H53" s="79"/>
+      <c r="I53" s="70"/>
       <c r="J53" s="18"/>
       <c r="K53" s="18"/>
       <c r="L53" s="18"/>
@@ -31031,55 +31031,55 @@
     <row r="55" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="18"/>
       <c r="B55" s="18"/>
-      <c r="C55" s="62"/>
-      <c r="D55" s="64"/>
-      <c r="E55" s="60"/>
+      <c r="C55" s="69"/>
+      <c r="D55" s="74"/>
+      <c r="E55" s="70"/>
       <c r="F55" s="18"/>
-      <c r="G55" s="62"/>
-      <c r="H55" s="100"/>
-      <c r="I55" s="60"/>
-      <c r="J55" s="60"/>
+      <c r="G55" s="69"/>
+      <c r="H55" s="75"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="70"/>
       <c r="K55" s="18"/>
-      <c r="L55" s="62"/>
-      <c r="M55" s="101"/>
-      <c r="N55" s="60"/>
-      <c r="O55" s="60"/>
+      <c r="L55" s="69"/>
+      <c r="M55" s="71"/>
+      <c r="N55" s="70"/>
+      <c r="O55" s="70"/>
       <c r="P55" s="18"/>
     </row>
     <row r="56" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="18"/>
       <c r="B56" s="18"/>
-      <c r="C56" s="60"/>
-      <c r="D56" s="60"/>
-      <c r="E56" s="60"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
       <c r="F56" s="18"/>
-      <c r="G56" s="60"/>
-      <c r="H56" s="60"/>
-      <c r="I56" s="60"/>
-      <c r="J56" s="60"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="70"/>
       <c r="K56" s="18"/>
-      <c r="L56" s="60"/>
-      <c r="M56" s="60"/>
-      <c r="N56" s="60"/>
-      <c r="O56" s="60"/>
+      <c r="L56" s="70"/>
+      <c r="M56" s="70"/>
+      <c r="N56" s="70"/>
+      <c r="O56" s="70"/>
       <c r="P56" s="18"/>
     </row>
     <row r="57" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="18"/>
       <c r="B57" s="18"/>
-      <c r="C57" s="60"/>
-      <c r="D57" s="60"/>
-      <c r="E57" s="60"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
       <c r="F57" s="18"/>
-      <c r="G57" s="60"/>
-      <c r="H57" s="60"/>
-      <c r="I57" s="60"/>
-      <c r="J57" s="60"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="70"/>
       <c r="K57" s="18"/>
-      <c r="L57" s="60"/>
-      <c r="M57" s="60"/>
-      <c r="N57" s="60"/>
-      <c r="O57" s="60"/>
+      <c r="L57" s="70"/>
+      <c r="M57" s="70"/>
+      <c r="N57" s="70"/>
+      <c r="O57" s="70"/>
       <c r="P57" s="18"/>
     </row>
     <row r="58" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -31103,37 +31103,37 @@
     <row r="59" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="18"/>
       <c r="B59" s="18"/>
-      <c r="C59" s="98"/>
-      <c r="D59" s="60"/>
-      <c r="E59" s="99"/>
-      <c r="F59" s="60"/>
-      <c r="G59" s="60"/>
-      <c r="H59" s="60"/>
-      <c r="I59" s="60"/>
-      <c r="J59" s="60"/>
-      <c r="K59" s="60"/>
-      <c r="L59" s="60"/>
-      <c r="M59" s="60"/>
-      <c r="N59" s="60"/>
-      <c r="O59" s="60"/>
+      <c r="C59" s="73"/>
+      <c r="D59" s="70"/>
+      <c r="E59" s="72"/>
+      <c r="F59" s="70"/>
+      <c r="G59" s="70"/>
+      <c r="H59" s="70"/>
+      <c r="I59" s="70"/>
+      <c r="J59" s="70"/>
+      <c r="K59" s="70"/>
+      <c r="L59" s="70"/>
+      <c r="M59" s="70"/>
+      <c r="N59" s="70"/>
+      <c r="O59" s="70"/>
       <c r="P59" s="18"/>
     </row>
     <row r="60" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="18"/>
       <c r="B60" s="18"/>
-      <c r="C60" s="60"/>
-      <c r="D60" s="60"/>
-      <c r="E60" s="60"/>
-      <c r="F60" s="60"/>
-      <c r="G60" s="60"/>
-      <c r="H60" s="60"/>
-      <c r="I60" s="60"/>
-      <c r="J60" s="60"/>
-      <c r="K60" s="60"/>
-      <c r="L60" s="60"/>
-      <c r="M60" s="60"/>
-      <c r="N60" s="60"/>
-      <c r="O60" s="60"/>
+      <c r="C60" s="70"/>
+      <c r="D60" s="70"/>
+      <c r="E60" s="70"/>
+      <c r="F60" s="70"/>
+      <c r="G60" s="70"/>
+      <c r="H60" s="70"/>
+      <c r="I60" s="70"/>
+      <c r="J60" s="70"/>
+      <c r="K60" s="70"/>
+      <c r="L60" s="70"/>
+      <c r="M60" s="70"/>
+      <c r="N60" s="70"/>
+      <c r="O60" s="70"/>
       <c r="P60" s="18"/>
     </row>
     <row r="61" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -31157,55 +31157,55 @@
     <row r="62" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
-      <c r="C62" s="62"/>
-      <c r="D62" s="60"/>
-      <c r="E62" s="102"/>
-      <c r="F62" s="60"/>
-      <c r="G62" s="60"/>
-      <c r="H62" s="60"/>
+      <c r="C62" s="69"/>
+      <c r="D62" s="70"/>
+      <c r="E62" s="78"/>
+      <c r="F62" s="70"/>
+      <c r="G62" s="70"/>
+      <c r="H62" s="70"/>
       <c r="I62" s="18"/>
-      <c r="J62" s="62"/>
-      <c r="K62" s="60"/>
-      <c r="L62" s="104"/>
-      <c r="M62" s="60"/>
-      <c r="N62" s="60"/>
-      <c r="O62" s="60"/>
+      <c r="J62" s="69"/>
+      <c r="K62" s="70"/>
+      <c r="L62" s="76"/>
+      <c r="M62" s="70"/>
+      <c r="N62" s="70"/>
+      <c r="O62" s="70"/>
       <c r="P62" s="18"/>
     </row>
     <row r="63" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
-      <c r="C63" s="60"/>
-      <c r="D63" s="60"/>
-      <c r="E63" s="60"/>
-      <c r="F63" s="60"/>
-      <c r="G63" s="60"/>
-      <c r="H63" s="60"/>
+      <c r="C63" s="70"/>
+      <c r="D63" s="70"/>
+      <c r="E63" s="70"/>
+      <c r="F63" s="70"/>
+      <c r="G63" s="70"/>
+      <c r="H63" s="70"/>
       <c r="I63" s="18"/>
-      <c r="J63" s="60"/>
-      <c r="K63" s="60"/>
-      <c r="L63" s="60"/>
-      <c r="M63" s="60"/>
-      <c r="N63" s="60"/>
-      <c r="O63" s="60"/>
+      <c r="J63" s="70"/>
+      <c r="K63" s="70"/>
+      <c r="L63" s="70"/>
+      <c r="M63" s="70"/>
+      <c r="N63" s="70"/>
+      <c r="O63" s="70"/>
       <c r="P63" s="18"/>
     </row>
     <row r="64" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
-      <c r="C64" s="60"/>
-      <c r="D64" s="60"/>
-      <c r="E64" s="60"/>
-      <c r="F64" s="60"/>
-      <c r="G64" s="60"/>
-      <c r="H64" s="60"/>
+      <c r="C64" s="70"/>
+      <c r="D64" s="70"/>
+      <c r="E64" s="70"/>
+      <c r="F64" s="70"/>
+      <c r="G64" s="70"/>
+      <c r="H64" s="70"/>
       <c r="I64" s="18"/>
-      <c r="J64" s="60"/>
-      <c r="K64" s="60"/>
-      <c r="L64" s="60"/>
-      <c r="M64" s="60"/>
-      <c r="N64" s="60"/>
-      <c r="O64" s="60"/>
+      <c r="J64" s="70"/>
+      <c r="K64" s="70"/>
+      <c r="L64" s="70"/>
+      <c r="M64" s="70"/>
+      <c r="N64" s="70"/>
+      <c r="O64" s="70"/>
       <c r="P64" s="18"/>
     </row>
     <row r="65" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -31229,39 +31229,39 @@
     <row r="66" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" spans="1:16" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="18"/>
-      <c r="B67" s="65"/>
-      <c r="C67" s="60"/>
-      <c r="D67" s="60"/>
-      <c r="E67" s="60"/>
-      <c r="F67" s="60"/>
-      <c r="G67" s="60"/>
-      <c r="H67" s="60"/>
-      <c r="I67" s="60"/>
-      <c r="J67" s="60"/>
-      <c r="K67" s="60"/>
-      <c r="L67" s="60"/>
-      <c r="M67" s="60"/>
-      <c r="N67" s="60"/>
-      <c r="O67" s="60"/>
-      <c r="P67" s="60"/>
+      <c r="B67" s="77"/>
+      <c r="C67" s="70"/>
+      <c r="D67" s="70"/>
+      <c r="E67" s="70"/>
+      <c r="F67" s="70"/>
+      <c r="G67" s="70"/>
+      <c r="H67" s="70"/>
+      <c r="I67" s="70"/>
+      <c r="J67" s="70"/>
+      <c r="K67" s="70"/>
+      <c r="L67" s="70"/>
+      <c r="M67" s="70"/>
+      <c r="N67" s="70"/>
+      <c r="O67" s="70"/>
+      <c r="P67" s="70"/>
     </row>
     <row r="68" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="18"/>
-      <c r="B68" s="65"/>
-      <c r="C68" s="60"/>
-      <c r="D68" s="60"/>
-      <c r="E68" s="60"/>
-      <c r="F68" s="60"/>
-      <c r="G68" s="60"/>
-      <c r="H68" s="60"/>
-      <c r="I68" s="60"/>
-      <c r="J68" s="60"/>
-      <c r="K68" s="60"/>
-      <c r="L68" s="60"/>
-      <c r="M68" s="60"/>
-      <c r="N68" s="60"/>
-      <c r="O68" s="60"/>
-      <c r="P68" s="60"/>
+      <c r="B68" s="77"/>
+      <c r="C68" s="70"/>
+      <c r="D68" s="70"/>
+      <c r="E68" s="70"/>
+      <c r="F68" s="70"/>
+      <c r="G68" s="70"/>
+      <c r="H68" s="70"/>
+      <c r="I68" s="70"/>
+      <c r="J68" s="70"/>
+      <c r="K68" s="70"/>
+      <c r="L68" s="70"/>
+      <c r="M68" s="70"/>
+      <c r="N68" s="70"/>
+      <c r="O68" s="70"/>
+      <c r="P68" s="70"/>
     </row>
     <row r="69" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="18"/>
@@ -31304,11 +31304,11 @@
       <c r="B71" s="18"/>
       <c r="C71" s="46"/>
       <c r="D71" s="18"/>
-      <c r="E71" s="62"/>
-      <c r="F71" s="60"/>
+      <c r="E71" s="69"/>
+      <c r="F71" s="70"/>
       <c r="G71" s="18"/>
-      <c r="H71" s="62"/>
-      <c r="I71" s="60"/>
+      <c r="H71" s="69"/>
+      <c r="I71" s="70"/>
       <c r="J71" s="18"/>
       <c r="K71" s="18"/>
       <c r="L71" s="18"/>
@@ -31322,11 +31322,11 @@
       <c r="B72" s="18"/>
       <c r="C72" s="46"/>
       <c r="D72" s="18"/>
-      <c r="E72" s="62"/>
-      <c r="F72" s="60"/>
+      <c r="E72" s="69"/>
+      <c r="F72" s="70"/>
       <c r="G72" s="18"/>
-      <c r="H72" s="62"/>
-      <c r="I72" s="60"/>
+      <c r="H72" s="69"/>
+      <c r="I72" s="70"/>
       <c r="J72" s="18"/>
       <c r="K72" s="18"/>
       <c r="L72" s="18"/>
@@ -31340,11 +31340,11 @@
       <c r="B73" s="18"/>
       <c r="C73" s="47"/>
       <c r="D73" s="18"/>
-      <c r="E73" s="59"/>
-      <c r="F73" s="60"/>
+      <c r="E73" s="79"/>
+      <c r="F73" s="70"/>
       <c r="G73" s="18"/>
-      <c r="H73" s="59"/>
-      <c r="I73" s="60"/>
+      <c r="H73" s="79"/>
+      <c r="I73" s="70"/>
       <c r="J73" s="18"/>
       <c r="K73" s="18"/>
       <c r="L73" s="18"/>
@@ -31374,55 +31374,55 @@
     <row r="75" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="18"/>
       <c r="B75" s="18"/>
-      <c r="C75" s="62"/>
-      <c r="D75" s="103"/>
-      <c r="E75" s="60"/>
+      <c r="C75" s="69"/>
+      <c r="D75" s="81"/>
+      <c r="E75" s="70"/>
       <c r="F75" s="18"/>
-      <c r="G75" s="62"/>
-      <c r="H75" s="100"/>
-      <c r="I75" s="60"/>
-      <c r="J75" s="60"/>
+      <c r="G75" s="69"/>
+      <c r="H75" s="75"/>
+      <c r="I75" s="70"/>
+      <c r="J75" s="70"/>
       <c r="K75" s="18"/>
-      <c r="L75" s="62"/>
-      <c r="M75" s="101"/>
-      <c r="N75" s="60"/>
-      <c r="O75" s="60"/>
+      <c r="L75" s="69"/>
+      <c r="M75" s="71"/>
+      <c r="N75" s="70"/>
+      <c r="O75" s="70"/>
       <c r="P75" s="18"/>
     </row>
     <row r="76" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="18"/>
       <c r="B76" s="18"/>
-      <c r="C76" s="60"/>
-      <c r="D76" s="60"/>
-      <c r="E76" s="60"/>
+      <c r="C76" s="70"/>
+      <c r="D76" s="70"/>
+      <c r="E76" s="70"/>
       <c r="F76" s="18"/>
-      <c r="G76" s="60"/>
-      <c r="H76" s="60"/>
-      <c r="I76" s="60"/>
-      <c r="J76" s="60"/>
+      <c r="G76" s="70"/>
+      <c r="H76" s="70"/>
+      <c r="I76" s="70"/>
+      <c r="J76" s="70"/>
       <c r="K76" s="18"/>
-      <c r="L76" s="60"/>
-      <c r="M76" s="60"/>
-      <c r="N76" s="60"/>
-      <c r="O76" s="60"/>
+      <c r="L76" s="70"/>
+      <c r="M76" s="70"/>
+      <c r="N76" s="70"/>
+      <c r="O76" s="70"/>
       <c r="P76" s="18"/>
     </row>
     <row r="77" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="18"/>
       <c r="B77" s="18"/>
-      <c r="C77" s="60"/>
-      <c r="D77" s="60"/>
-      <c r="E77" s="60"/>
+      <c r="C77" s="70"/>
+      <c r="D77" s="70"/>
+      <c r="E77" s="70"/>
       <c r="F77" s="18"/>
-      <c r="G77" s="60"/>
-      <c r="H77" s="60"/>
-      <c r="I77" s="60"/>
-      <c r="J77" s="60"/>
+      <c r="G77" s="70"/>
+      <c r="H77" s="70"/>
+      <c r="I77" s="70"/>
+      <c r="J77" s="70"/>
       <c r="K77" s="18"/>
-      <c r="L77" s="60"/>
-      <c r="M77" s="60"/>
-      <c r="N77" s="60"/>
-      <c r="O77" s="60"/>
+      <c r="L77" s="70"/>
+      <c r="M77" s="70"/>
+      <c r="N77" s="70"/>
+      <c r="O77" s="70"/>
       <c r="P77" s="18"/>
     </row>
     <row r="78" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -31446,37 +31446,37 @@
     <row r="79" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="18"/>
       <c r="B79" s="18"/>
-      <c r="C79" s="98"/>
-      <c r="D79" s="60"/>
-      <c r="E79" s="99"/>
-      <c r="F79" s="60"/>
-      <c r="G79" s="60"/>
-      <c r="H79" s="60"/>
-      <c r="I79" s="60"/>
-      <c r="J79" s="60"/>
-      <c r="K79" s="60"/>
-      <c r="L79" s="60"/>
-      <c r="M79" s="60"/>
-      <c r="N79" s="60"/>
-      <c r="O79" s="60"/>
+      <c r="C79" s="73"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="72"/>
+      <c r="F79" s="70"/>
+      <c r="G79" s="70"/>
+      <c r="H79" s="70"/>
+      <c r="I79" s="70"/>
+      <c r="J79" s="70"/>
+      <c r="K79" s="70"/>
+      <c r="L79" s="70"/>
+      <c r="M79" s="70"/>
+      <c r="N79" s="70"/>
+      <c r="O79" s="70"/>
       <c r="P79" s="18"/>
     </row>
     <row r="80" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="18"/>
       <c r="B80" s="18"/>
-      <c r="C80" s="60"/>
-      <c r="D80" s="60"/>
-      <c r="E80" s="60"/>
-      <c r="F80" s="60"/>
-      <c r="G80" s="60"/>
-      <c r="H80" s="60"/>
-      <c r="I80" s="60"/>
-      <c r="J80" s="60"/>
-      <c r="K80" s="60"/>
-      <c r="L80" s="60"/>
-      <c r="M80" s="60"/>
-      <c r="N80" s="60"/>
-      <c r="O80" s="60"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="70"/>
+      <c r="G80" s="70"/>
+      <c r="H80" s="70"/>
+      <c r="I80" s="70"/>
+      <c r="J80" s="70"/>
+      <c r="K80" s="70"/>
+      <c r="L80" s="70"/>
+      <c r="M80" s="70"/>
+      <c r="N80" s="70"/>
+      <c r="O80" s="70"/>
       <c r="P80" s="18"/>
     </row>
     <row r="81" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -31500,55 +31500,55 @@
     <row r="82" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="18"/>
       <c r="B82" s="18"/>
-      <c r="C82" s="62"/>
-      <c r="D82" s="60"/>
-      <c r="E82" s="102"/>
-      <c r="F82" s="60"/>
-      <c r="G82" s="60"/>
-      <c r="H82" s="60"/>
+      <c r="C82" s="69"/>
+      <c r="D82" s="70"/>
+      <c r="E82" s="78"/>
+      <c r="F82" s="70"/>
+      <c r="G82" s="70"/>
+      <c r="H82" s="70"/>
       <c r="I82" s="18"/>
-      <c r="J82" s="62"/>
-      <c r="K82" s="60"/>
-      <c r="L82" s="96"/>
-      <c r="M82" s="60"/>
-      <c r="N82" s="60"/>
-      <c r="O82" s="60"/>
+      <c r="J82" s="69"/>
+      <c r="K82" s="70"/>
+      <c r="L82" s="80"/>
+      <c r="M82" s="70"/>
+      <c r="N82" s="70"/>
+      <c r="O82" s="70"/>
       <c r="P82" s="18"/>
     </row>
     <row r="83" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="18"/>
       <c r="B83" s="18"/>
-      <c r="C83" s="60"/>
-      <c r="D83" s="60"/>
-      <c r="E83" s="60"/>
-      <c r="F83" s="60"/>
-      <c r="G83" s="60"/>
-      <c r="H83" s="60"/>
+      <c r="C83" s="70"/>
+      <c r="D83" s="70"/>
+      <c r="E83" s="70"/>
+      <c r="F83" s="70"/>
+      <c r="G83" s="70"/>
+      <c r="H83" s="70"/>
       <c r="I83" s="18"/>
-      <c r="J83" s="60"/>
-      <c r="K83" s="60"/>
-      <c r="L83" s="60"/>
-      <c r="M83" s="60"/>
-      <c r="N83" s="60"/>
-      <c r="O83" s="60"/>
+      <c r="J83" s="70"/>
+      <c r="K83" s="70"/>
+      <c r="L83" s="70"/>
+      <c r="M83" s="70"/>
+      <c r="N83" s="70"/>
+      <c r="O83" s="70"/>
       <c r="P83" s="18"/>
     </row>
     <row r="84" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="18"/>
       <c r="B84" s="18"/>
-      <c r="C84" s="60"/>
-      <c r="D84" s="60"/>
-      <c r="E84" s="60"/>
-      <c r="F84" s="60"/>
-      <c r="G84" s="60"/>
-      <c r="H84" s="60"/>
+      <c r="C84" s="70"/>
+      <c r="D84" s="70"/>
+      <c r="E84" s="70"/>
+      <c r="F84" s="70"/>
+      <c r="G84" s="70"/>
+      <c r="H84" s="70"/>
       <c r="I84" s="18"/>
-      <c r="J84" s="60"/>
-      <c r="K84" s="60"/>
-      <c r="L84" s="60"/>
-      <c r="M84" s="60"/>
-      <c r="N84" s="60"/>
-      <c r="O84" s="60"/>
+      <c r="J84" s="70"/>
+      <c r="K84" s="70"/>
+      <c r="L84" s="70"/>
+      <c r="M84" s="70"/>
+      <c r="N84" s="70"/>
+      <c r="O84" s="70"/>
       <c r="P84" s="18"/>
     </row>
     <row r="85" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -31573,21 +31573,21 @@
     </row>
     <row r="87" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A87" s="18"/>
-      <c r="B87" s="65"/>
-      <c r="C87" s="60"/>
-      <c r="D87" s="60"/>
-      <c r="E87" s="60"/>
-      <c r="F87" s="60"/>
-      <c r="G87" s="60"/>
-      <c r="H87" s="60"/>
-      <c r="I87" s="60"/>
-      <c r="J87" s="60"/>
-      <c r="K87" s="60"/>
-      <c r="L87" s="60"/>
-      <c r="M87" s="60"/>
-      <c r="N87" s="60"/>
-      <c r="O87" s="60"/>
-      <c r="P87" s="60"/>
+      <c r="B87" s="77"/>
+      <c r="C87" s="70"/>
+      <c r="D87" s="70"/>
+      <c r="E87" s="70"/>
+      <c r="F87" s="70"/>
+      <c r="G87" s="70"/>
+      <c r="H87" s="70"/>
+      <c r="I87" s="70"/>
+      <c r="J87" s="70"/>
+      <c r="K87" s="70"/>
+      <c r="L87" s="70"/>
+      <c r="M87" s="70"/>
+      <c r="N87" s="70"/>
+      <c r="O87" s="70"/>
+      <c r="P87" s="70"/>
     </row>
     <row r="88" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="18"/>
@@ -31630,11 +31630,11 @@
       <c r="B90" s="18"/>
       <c r="C90" s="46"/>
       <c r="D90" s="18"/>
-      <c r="E90" s="62"/>
-      <c r="F90" s="60"/>
+      <c r="E90" s="69"/>
+      <c r="F90" s="70"/>
       <c r="G90" s="18"/>
-      <c r="H90" s="62"/>
-      <c r="I90" s="60"/>
+      <c r="H90" s="69"/>
+      <c r="I90" s="70"/>
       <c r="J90" s="18"/>
       <c r="K90" s="18"/>
       <c r="L90" s="18"/>
@@ -31648,11 +31648,11 @@
       <c r="B91" s="18"/>
       <c r="C91" s="47"/>
       <c r="D91" s="18"/>
-      <c r="E91" s="59"/>
-      <c r="F91" s="60"/>
+      <c r="E91" s="79"/>
+      <c r="F91" s="70"/>
       <c r="G91" s="18"/>
-      <c r="H91" s="59"/>
-      <c r="I91" s="60"/>
+      <c r="H91" s="79"/>
+      <c r="I91" s="70"/>
       <c r="J91" s="18"/>
       <c r="K91" s="18"/>
       <c r="L91" s="18"/>
@@ -31682,55 +31682,55 @@
     <row r="93" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="18"/>
       <c r="B93" s="18"/>
-      <c r="C93" s="62"/>
-      <c r="D93" s="100"/>
-      <c r="E93" s="60"/>
+      <c r="C93" s="69"/>
+      <c r="D93" s="75"/>
+      <c r="E93" s="70"/>
       <c r="F93" s="18"/>
-      <c r="G93" s="62"/>
-      <c r="H93" s="100"/>
-      <c r="I93" s="60"/>
-      <c r="J93" s="60"/>
+      <c r="G93" s="69"/>
+      <c r="H93" s="75"/>
+      <c r="I93" s="70"/>
+      <c r="J93" s="70"/>
       <c r="K93" s="18"/>
-      <c r="L93" s="62"/>
-      <c r="M93" s="97"/>
-      <c r="N93" s="60"/>
-      <c r="O93" s="60"/>
+      <c r="L93" s="69"/>
+      <c r="M93" s="82"/>
+      <c r="N93" s="70"/>
+      <c r="O93" s="70"/>
       <c r="P93" s="18"/>
     </row>
     <row r="94" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="18"/>
       <c r="B94" s="18"/>
-      <c r="C94" s="60"/>
-      <c r="D94" s="60"/>
-      <c r="E94" s="60"/>
+      <c r="C94" s="70"/>
+      <c r="D94" s="70"/>
+      <c r="E94" s="70"/>
       <c r="F94" s="18"/>
-      <c r="G94" s="60"/>
-      <c r="H94" s="60"/>
-      <c r="I94" s="60"/>
-      <c r="J94" s="60"/>
+      <c r="G94" s="70"/>
+      <c r="H94" s="70"/>
+      <c r="I94" s="70"/>
+      <c r="J94" s="70"/>
       <c r="K94" s="18"/>
-      <c r="L94" s="60"/>
-      <c r="M94" s="60"/>
-      <c r="N94" s="60"/>
-      <c r="O94" s="60"/>
+      <c r="L94" s="70"/>
+      <c r="M94" s="70"/>
+      <c r="N94" s="70"/>
+      <c r="O94" s="70"/>
       <c r="P94" s="18"/>
     </row>
     <row r="95" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="18"/>
       <c r="B95" s="18"/>
-      <c r="C95" s="60"/>
-      <c r="D95" s="60"/>
-      <c r="E95" s="60"/>
+      <c r="C95" s="70"/>
+      <c r="D95" s="70"/>
+      <c r="E95" s="70"/>
       <c r="F95" s="18"/>
-      <c r="G95" s="60"/>
-      <c r="H95" s="60"/>
-      <c r="I95" s="60"/>
-      <c r="J95" s="60"/>
+      <c r="G95" s="70"/>
+      <c r="H95" s="70"/>
+      <c r="I95" s="70"/>
+      <c r="J95" s="70"/>
       <c r="K95" s="18"/>
-      <c r="L95" s="60"/>
-      <c r="M95" s="60"/>
-      <c r="N95" s="60"/>
-      <c r="O95" s="60"/>
+      <c r="L95" s="70"/>
+      <c r="M95" s="70"/>
+      <c r="N95" s="70"/>
+      <c r="O95" s="70"/>
       <c r="P95" s="18"/>
     </row>
     <row r="96" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -31754,37 +31754,37 @@
     <row r="97" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="18"/>
       <c r="B97" s="18"/>
-      <c r="C97" s="98"/>
-      <c r="D97" s="60"/>
-      <c r="E97" s="99"/>
-      <c r="F97" s="60"/>
-      <c r="G97" s="60"/>
-      <c r="H97" s="60"/>
-      <c r="I97" s="60"/>
-      <c r="J97" s="60"/>
-      <c r="K97" s="60"/>
-      <c r="L97" s="60"/>
-      <c r="M97" s="60"/>
-      <c r="N97" s="60"/>
-      <c r="O97" s="60"/>
+      <c r="C97" s="73"/>
+      <c r="D97" s="70"/>
+      <c r="E97" s="72"/>
+      <c r="F97" s="70"/>
+      <c r="G97" s="70"/>
+      <c r="H97" s="70"/>
+      <c r="I97" s="70"/>
+      <c r="J97" s="70"/>
+      <c r="K97" s="70"/>
+      <c r="L97" s="70"/>
+      <c r="M97" s="70"/>
+      <c r="N97" s="70"/>
+      <c r="O97" s="70"/>
       <c r="P97" s="18"/>
     </row>
     <row r="98" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="18"/>
       <c r="B98" s="18"/>
-      <c r="C98" s="60"/>
-      <c r="D98" s="60"/>
-      <c r="E98" s="60"/>
-      <c r="F98" s="60"/>
-      <c r="G98" s="60"/>
-      <c r="H98" s="60"/>
-      <c r="I98" s="60"/>
-      <c r="J98" s="60"/>
-      <c r="K98" s="60"/>
-      <c r="L98" s="60"/>
-      <c r="M98" s="60"/>
-      <c r="N98" s="60"/>
-      <c r="O98" s="60"/>
+      <c r="C98" s="70"/>
+      <c r="D98" s="70"/>
+      <c r="E98" s="70"/>
+      <c r="F98" s="70"/>
+      <c r="G98" s="70"/>
+      <c r="H98" s="70"/>
+      <c r="I98" s="70"/>
+      <c r="J98" s="70"/>
+      <c r="K98" s="70"/>
+      <c r="L98" s="70"/>
+      <c r="M98" s="70"/>
+      <c r="N98" s="70"/>
+      <c r="O98" s="70"/>
       <c r="P98" s="18"/>
     </row>
     <row r="99" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -31808,55 +31808,55 @@
     <row r="100" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="18"/>
       <c r="B100" s="18"/>
-      <c r="C100" s="62"/>
-      <c r="D100" s="60"/>
-      <c r="E100" s="95"/>
-      <c r="F100" s="60"/>
-      <c r="G100" s="60"/>
-      <c r="H100" s="60"/>
+      <c r="C100" s="69"/>
+      <c r="D100" s="70"/>
+      <c r="E100" s="83"/>
+      <c r="F100" s="70"/>
+      <c r="G100" s="70"/>
+      <c r="H100" s="70"/>
       <c r="I100" s="18"/>
-      <c r="J100" s="62"/>
-      <c r="K100" s="60"/>
-      <c r="L100" s="96"/>
-      <c r="M100" s="60"/>
-      <c r="N100" s="60"/>
-      <c r="O100" s="60"/>
+      <c r="J100" s="69"/>
+      <c r="K100" s="70"/>
+      <c r="L100" s="80"/>
+      <c r="M100" s="70"/>
+      <c r="N100" s="70"/>
+      <c r="O100" s="70"/>
       <c r="P100" s="18"/>
     </row>
     <row r="101" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="18"/>
       <c r="B101" s="18"/>
-      <c r="C101" s="60"/>
-      <c r="D101" s="60"/>
-      <c r="E101" s="60"/>
-      <c r="F101" s="60"/>
-      <c r="G101" s="60"/>
-      <c r="H101" s="60"/>
+      <c r="C101" s="70"/>
+      <c r="D101" s="70"/>
+      <c r="E101" s="70"/>
+      <c r="F101" s="70"/>
+      <c r="G101" s="70"/>
+      <c r="H101" s="70"/>
       <c r="I101" s="18"/>
-      <c r="J101" s="60"/>
-      <c r="K101" s="60"/>
-      <c r="L101" s="60"/>
-      <c r="M101" s="60"/>
-      <c r="N101" s="60"/>
-      <c r="O101" s="60"/>
+      <c r="J101" s="70"/>
+      <c r="K101" s="70"/>
+      <c r="L101" s="70"/>
+      <c r="M101" s="70"/>
+      <c r="N101" s="70"/>
+      <c r="O101" s="70"/>
       <c r="P101" s="18"/>
     </row>
     <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="18"/>
       <c r="B102" s="18"/>
-      <c r="C102" s="60"/>
-      <c r="D102" s="60"/>
-      <c r="E102" s="60"/>
-      <c r="F102" s="60"/>
-      <c r="G102" s="60"/>
-      <c r="H102" s="60"/>
+      <c r="C102" s="70"/>
+      <c r="D102" s="70"/>
+      <c r="E102" s="70"/>
+      <c r="F102" s="70"/>
+      <c r="G102" s="70"/>
+      <c r="H102" s="70"/>
       <c r="I102" s="18"/>
-      <c r="J102" s="60"/>
-      <c r="K102" s="60"/>
-      <c r="L102" s="60"/>
-      <c r="M102" s="60"/>
-      <c r="N102" s="60"/>
-      <c r="O102" s="60"/>
+      <c r="J102" s="70"/>
+      <c r="K102" s="70"/>
+      <c r="L102" s="70"/>
+      <c r="M102" s="70"/>
+      <c r="N102" s="70"/>
+      <c r="O102" s="70"/>
       <c r="P102" s="18"/>
     </row>
     <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -31894,21 +31894,21 @@
       <c r="P104" s="18"/>
     </row>
     <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B105" s="65"/>
-      <c r="C105" s="60"/>
-      <c r="D105" s="60"/>
-      <c r="E105" s="60"/>
-      <c r="F105" s="60"/>
-      <c r="G105" s="60"/>
-      <c r="H105" s="60"/>
-      <c r="I105" s="60"/>
-      <c r="J105" s="60"/>
-      <c r="K105" s="60"/>
-      <c r="L105" s="60"/>
-      <c r="M105" s="60"/>
-      <c r="N105" s="60"/>
-      <c r="O105" s="60"/>
-      <c r="P105" s="60"/>
+      <c r="B105" s="77"/>
+      <c r="C105" s="70"/>
+      <c r="D105" s="70"/>
+      <c r="E105" s="70"/>
+      <c r="F105" s="70"/>
+      <c r="G105" s="70"/>
+      <c r="H105" s="70"/>
+      <c r="I105" s="70"/>
+      <c r="J105" s="70"/>
+      <c r="K105" s="70"/>
+      <c r="L105" s="70"/>
+      <c r="M105" s="70"/>
+      <c r="N105" s="70"/>
+      <c r="O105" s="70"/>
+      <c r="P105" s="70"/>
     </row>
     <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -32820,38 +32820,60 @@
     <row r="1013" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="L55:L57"/>
-    <mergeCell ref="M55:O57"/>
-    <mergeCell ref="E59:O60"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="C59:D60"/>
-    <mergeCell ref="D55:E57"/>
-    <mergeCell ref="G55:G57"/>
-    <mergeCell ref="H55:J57"/>
-    <mergeCell ref="C62:D64"/>
-    <mergeCell ref="J62:K64"/>
-    <mergeCell ref="L62:O64"/>
-    <mergeCell ref="B67:P67"/>
-    <mergeCell ref="B68:P68"/>
-    <mergeCell ref="E62:H64"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="M75:O77"/>
-    <mergeCell ref="E79:O80"/>
-    <mergeCell ref="C79:D80"/>
-    <mergeCell ref="C82:D84"/>
-    <mergeCell ref="E82:H84"/>
-    <mergeCell ref="J82:K84"/>
-    <mergeCell ref="L82:O84"/>
-    <mergeCell ref="C75:C77"/>
-    <mergeCell ref="D75:E77"/>
-    <mergeCell ref="G75:G77"/>
-    <mergeCell ref="H75:J77"/>
-    <mergeCell ref="L75:L77"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="J41:K43"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="L41:O43"/>
+    <mergeCell ref="B46:P46"/>
+    <mergeCell ref="E41:H43"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="D34:E36"/>
+    <mergeCell ref="G34:G36"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="C41:D43"/>
+    <mergeCell ref="H34:J36"/>
+    <mergeCell ref="L34:L36"/>
+    <mergeCell ref="M34:O36"/>
+    <mergeCell ref="E38:O39"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="C22:D24"/>
+    <mergeCell ref="E22:H24"/>
+    <mergeCell ref="J22:K24"/>
+    <mergeCell ref="L22:O24"/>
+    <mergeCell ref="B27:P27"/>
+    <mergeCell ref="L15:L17"/>
+    <mergeCell ref="M15:O17"/>
+    <mergeCell ref="E19:O20"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="D15:E17"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="H15:J17"/>
+    <mergeCell ref="B6:P6"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="C100:D102"/>
+    <mergeCell ref="E100:H102"/>
+    <mergeCell ref="J100:K102"/>
+    <mergeCell ref="L100:O102"/>
+    <mergeCell ref="B105:P105"/>
     <mergeCell ref="B87:P87"/>
     <mergeCell ref="H90:I90"/>
     <mergeCell ref="L93:L95"/>
@@ -32865,60 +32887,38 @@
     <mergeCell ref="D93:E95"/>
     <mergeCell ref="G93:G95"/>
     <mergeCell ref="H93:J95"/>
-    <mergeCell ref="C100:D102"/>
-    <mergeCell ref="E100:H102"/>
-    <mergeCell ref="J100:K102"/>
-    <mergeCell ref="L100:O102"/>
-    <mergeCell ref="B105:P105"/>
-    <mergeCell ref="B6:P6"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="D15:E17"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="H15:J17"/>
-    <mergeCell ref="L15:L17"/>
-    <mergeCell ref="M15:O17"/>
-    <mergeCell ref="E19:O20"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="C22:D24"/>
-    <mergeCell ref="E22:H24"/>
-    <mergeCell ref="J22:K24"/>
-    <mergeCell ref="L22:O24"/>
-    <mergeCell ref="B27:P27"/>
-    <mergeCell ref="H34:J36"/>
-    <mergeCell ref="L34:L36"/>
-    <mergeCell ref="M34:O36"/>
-    <mergeCell ref="E38:O39"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="D34:E36"/>
-    <mergeCell ref="G34:G36"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="C41:D43"/>
-    <mergeCell ref="L41:O43"/>
-    <mergeCell ref="B46:P46"/>
-    <mergeCell ref="E41:H43"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="J41:K43"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="M75:O77"/>
+    <mergeCell ref="E79:O80"/>
+    <mergeCell ref="C79:D80"/>
+    <mergeCell ref="C82:D84"/>
+    <mergeCell ref="E82:H84"/>
+    <mergeCell ref="J82:K84"/>
+    <mergeCell ref="L82:O84"/>
+    <mergeCell ref="C75:C77"/>
+    <mergeCell ref="D75:E77"/>
+    <mergeCell ref="G75:G77"/>
+    <mergeCell ref="H75:J77"/>
+    <mergeCell ref="L75:L77"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="C62:D64"/>
+    <mergeCell ref="J62:K64"/>
+    <mergeCell ref="L62:O64"/>
+    <mergeCell ref="B67:P67"/>
+    <mergeCell ref="B68:P68"/>
+    <mergeCell ref="E62:H64"/>
+    <mergeCell ref="L55:L57"/>
+    <mergeCell ref="M55:O57"/>
+    <mergeCell ref="E59:O60"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="C59:D60"/>
+    <mergeCell ref="D55:E57"/>
+    <mergeCell ref="G55:G57"/>
+    <mergeCell ref="H55:J57"/>
   </mergeCells>
   <conditionalFormatting sqref="H10:I11 H50">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
